--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486823_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486823_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.3975</v>
+        <v>9.353899999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>11.0455</v>
+        <v>8.722</v>
       </c>
       <c r="F2" t="n">
-        <v>1.352</v>
+        <v>0.6319</v>
       </c>
       <c r="G2" t="n">
         <v>4.3512</v>
@@ -610,13 +610,13 @@
         <v>1.1585</v>
       </c>
       <c r="S2" t="n">
-        <v>5.7261</v>
+        <v>2.6824</v>
       </c>
       <c r="T2" t="n">
-        <v>3.9434</v>
+        <v>1.6199</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7826</v>
+        <v>1.0625</v>
       </c>
       <c r="V2" t="n">
         <v>2.1271</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6832</v>
+        <v>6.8181</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4072</v>
+        <v>6.3931</v>
       </c>
       <c r="F3" t="n">
-        <v>0.276</v>
+        <v>0.425</v>
       </c>
       <c r="G3" t="n">
         <v>2.5618</v>
@@ -688,13 +688,13 @@
         <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7282</v>
+        <v>0.4068</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0209</v>
+        <v>-0.0349</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2928</v>
+        <v>0.4418</v>
       </c>
       <c r="V3" t="n">
         <v>2.498</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1158</v>
+        <v>6.7764</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8706</v>
+        <v>5.96</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2452</v>
+        <v>0.8163</v>
       </c>
       <c r="G4" t="n">
         <v>1.4553</v>
@@ -766,13 +766,13 @@
         <v>2.1239</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2815</v>
+        <v>1.379</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3039</v>
+        <v>0.7855</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0224</v>
+        <v>0.5935</v>
       </c>
       <c r="V4" t="n">
         <v>2.7836</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2575</v>
+        <v>-0.0405</v>
       </c>
       <c r="E5" t="n">
         <v>0.5977</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3401</v>
+        <v>-0.6381</v>
       </c>
       <c r="G5" t="n">
         <v>0.3696</v>
@@ -844,13 +844,13 @@
         <v>1.5446</v>
       </c>
       <c r="S5" t="n">
-        <v>0.822</v>
+        <v>0.5241</v>
       </c>
       <c r="T5" t="n">
         <v>0.1927</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6293</v>
+        <v>0.3313</v>
       </c>
       <c r="V5" t="n">
         <v>-1.5133</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8534</v>
+        <v>-0.2245</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0455</v>
+        <v>1.2524</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.899</v>
+        <v>-1.4768</v>
       </c>
       <c r="G6" t="n">
         <v>1.569</v>
@@ -922,13 +922,13 @@
         <v>1.1585</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1601</v>
+        <v>0.4688</v>
       </c>
       <c r="T6" t="n">
-        <v>0.11</v>
+        <v>0.3169</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2702</v>
+        <v>0.152</v>
       </c>
       <c r="V6" t="n">
         <v>-2.4554</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. LAGUNA RODRIGUEZ</t>
+          <t>V. NEGRE FABREGAT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2691</v>
+        <v>-1.1914</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7332</v>
+        <v>-1.2125</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5359</v>
+        <v>0.021</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.63</v>
+        <v>-2.9653</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1929</v>
+        <v>-2.4069</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5629</v>
+        <v>-0.5583</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7603</v>
+        <v>-1.9574</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.9857</v>
+        <v>-1.2341</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2253</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8697</v>
+        <v>-1.0079</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2072</v>
+        <v>-1.1728</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6624</v>
+        <v>0.165</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5792</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0094</v>
+        <v>0.0828</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9926</v>
+        <v>0.2204</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0168</v>
+        <v>-0.1376</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2277</v>
+        <v>1.8842</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.4554</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2277</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. NEGRE FABREGAT</t>
+          <t>I. CHAMERO CASTELLANOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4398</v>
+        <v>-1.2073</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2125</v>
+        <v>-1.0761</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2273</v>
+        <v>-0.1312</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.9653</v>
+        <v>-1.0352</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.4069</v>
+        <v>-0.2553</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5583</v>
+        <v>-0.7799</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.9574</v>
+        <v>-0.6281</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2341</v>
+        <v>0.0207</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.6488</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0079</v>
+        <v>-0.4071</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1728</v>
+        <v>-0.2759</v>
       </c>
       <c r="O8" t="n">
-        <v>0.165</v>
+        <v>-0.1311</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1931</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7377</v>
+        <v>0.1931</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1655</v>
+        <v>0.3379</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2204</v>
+        <v>0.2551</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3859</v>
+        <v>0.0828</v>
       </c>
       <c r="V8" t="n">
-        <v>1.8842</v>
+        <v>1.2277</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4554</v>
+        <v>1.2277</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. CHAMERO CASTELLANOS</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5673</v>
+        <v>-1.6691</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3864</v>
+        <v>-2.4863</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1809</v>
+        <v>0.8171</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0352</v>
+        <v>-1.4181</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2553</v>
+        <v>-1.5379</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7799</v>
+        <v>0.1198</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6281</v>
+        <v>-1.0173</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0207</v>
+        <v>-0.572</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6488</v>
+        <v>-0.4453</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4071</v>
+        <v>-0.4008</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2759</v>
+        <v>-0.9659</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1311</v>
+        <v>0.5651</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7377</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1931</v>
+        <v>0.7723</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0221</v>
+        <v>1.193</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0552</v>
+        <v>0.4618</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0331</v>
+        <v>0.7312</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2277</v>
+        <v>-0.2856</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>M. LAGUNA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6539</v>
+        <v>-1.8648</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6449</v>
+        <v>-1.3537</v>
       </c>
       <c r="F10" t="n">
-        <v>0.991</v>
+        <v>-0.5111</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4181</v>
+        <v>-1.63</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5379</v>
+        <v>-2.1929</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1198</v>
+        <v>0.5629</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0173</v>
+        <v>-0.7603</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.572</v>
+        <v>-1.9857</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4453</v>
+        <v>1.2253</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4008</v>
+        <v>-0.8697</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9659</v>
+        <v>-0.2072</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5651</v>
+        <v>-0.6624</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1585</v>
+        <v>0.5792</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7723</v>
+        <v>1.5446</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2083</v>
+        <v>0.4137</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3032</v>
+        <v>0.372</v>
       </c>
       <c r="U10" t="n">
-        <v>0.905</v>
+        <v>0.0416</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2178</v>
+        <v>-3.0221</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7035</v>
+        <v>-3.2347</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4857</v>
+        <v>0.2125</v>
       </c>
       <c r="G11" t="n">
         <v>-4.3599</v>
@@ -1312,13 +1312,13 @@
         <v>1.9308</v>
       </c>
       <c r="S11" t="n">
-        <v>1.142</v>
+        <v>1.3378</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3028</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4527</v>
+        <v>13.7287</v>
       </c>
       <c r="E12" t="n">
-        <v>13.286</v>
+        <v>13.5619</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1667000000000004</v>
+        <v>0.1666000000000002</v>
       </c>
       <c r="G12" t="n">
         <v>-1.101599999999999</v>
@@ -1363,13 +1363,13 @@
         <v>3.3797</v>
       </c>
       <c r="J12" t="n">
-        <v>9.287599999999998</v>
+        <v>9.287599999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>2.075299999999999</v>
+        <v>2.0753</v>
       </c>
       <c r="L12" t="n">
-        <v>7.2122</v>
+        <v>7.212199999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-10.3893</v>
@@ -1381,7 +1381,7 @@
         <v>-3.8324</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9653</v>
+        <v>0.9652999999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.5502</v>
@@ -1390,22 +1390,22 @@
         <v>13.5155</v>
       </c>
       <c r="S12" t="n">
-        <v>8.550399999999998</v>
+        <v>8.8263</v>
       </c>
       <c r="T12" t="n">
-        <v>4.685100000000001</v>
+        <v>4.9611</v>
       </c>
       <c r="U12" t="n">
         <v>3.8651</v>
       </c>
       <c r="V12" t="n">
-        <v>5.0386</v>
+        <v>5.038599999999999</v>
       </c>
       <c r="W12" t="n">
         <v>11.8634</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.8248</v>
+        <v>-6.824800000000002</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.0631</v>
+        <v>6.6603</v>
       </c>
       <c r="E13" t="n">
-        <v>6.8506</v>
+        <v>6.6437</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2126</v>
+        <v>0.0166</v>
       </c>
       <c r="G13" t="n">
         <v>1.0241</v>
@@ -1468,13 +1468,13 @@
         <v>1.7377</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3753</v>
+        <v>-0.0276</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0558</v>
+        <v>-0.2626</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4311</v>
+        <v>0.2351</v>
       </c>
       <c r="V13" t="n">
         <v>3.9261</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0329</v>
+        <v>2.9847</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1306</v>
+        <v>2.8204</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0977</v>
+        <v>0.1644</v>
       </c>
       <c r="G14" t="n">
         <v>3.0481</v>
@@ -1546,13 +1546,13 @@
         <v>2.1239</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.131</v>
+        <v>-1.1792</v>
       </c>
       <c r="T14" t="n">
-        <v>0.165</v>
+        <v>-0.1453</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2959</v>
+        <v>-1.0339</v>
       </c>
       <c r="V14" t="n">
         <v>-0.0426</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4716</v>
+        <v>0.4965</v>
       </c>
       <c r="E15" t="n">
         <v>-0.06900000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5406</v>
+        <v>0.5654</v>
       </c>
       <c r="G15" t="n">
         <v>0.3172</v>
@@ -1624,13 +1624,13 @@
         <v>0.3862</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2317</v>
+        <v>-0.2069</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1213</v>
+        <v>-0.0965</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8813</v>
+        <v>-0.7723</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1544</v>
+        <v>0.051</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0358</v>
+        <v>-0.8234</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2565</v>
@@ -1702,13 +1702,13 @@
         <v>1.3515</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8882</v>
+        <v>-0.7792</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5797</v>
+        <v>-0.6831</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3085</v>
+        <v>-0.0961</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1228</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6286</v>
+        <v>-1.1267</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8694</v>
+        <v>2.2831</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.498</v>
+        <v>-3.4098</v>
       </c>
       <c r="G17" t="n">
         <v>3.109</v>
@@ -1780,13 +1780,13 @@
         <v>1.1585</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7154</v>
+        <v>-1.2135</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0485</v>
+        <v>-0.6348</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6669</v>
+        <v>-0.5787</v>
       </c>
       <c r="V17" t="n">
         <v>-2.2499</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.669</v>
+        <v>-2.8443</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5683</v>
+        <v>-0.1547</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.1007</v>
+        <v>-2.6896</v>
       </c>
       <c r="G18" t="n">
         <v>1.2441</v>
@@ -1858,13 +1858,13 @@
         <v>1.7377</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.4935</v>
+        <v>-1.6687</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1588</v>
+        <v>-0.7451</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3346</v>
+        <v>-0.9236</v>
       </c>
       <c r="V18" t="n">
         <v>-3.192</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.1491</v>
+        <v>-4.5616</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.1194</v>
+        <v>-2.7057</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0298</v>
+        <v>-1.8559</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1476</v>
@@ -1936,13 +1936,13 @@
         <v>0.7723</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3185</v>
+        <v>-0.731</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.607</v>
+        <v>-0.1933</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7115</v>
+        <v>-0.5377</v>
       </c>
       <c r="V19" t="n">
         <v>-2.4554</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.5207</v>
+        <v>-5.0174</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.4562</v>
+        <v>-4.3528</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0646</v>
+        <v>-0.6646</v>
       </c>
       <c r="G20" t="n">
         <v>-2.6581</v>
@@ -2014,13 +2014,13 @@
         <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2411</v>
+        <v>-0.7377</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8277</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4134</v>
+        <v>-0.0134</v>
       </c>
       <c r="V20" t="n">
         <v>2.047</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.1716</v>
+        <v>-7.893</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.9588</v>
+        <v>-4.6828</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.2128</v>
+        <v>-3.2102</v>
       </c>
       <c r="G21" t="n">
         <v>-2.5788</v>
@@ -2092,13 +2092,13 @@
         <v>2.1239</v>
       </c>
       <c r="S21" t="n">
-        <v>0.09379999999999999</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3578</v>
+        <v>-0.3662</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.264</v>
+        <v>-0.2613</v>
       </c>
       <c r="V21" t="n">
         <v>-2.949</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-13.4527</v>
+        <v>-12.0738</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1667000000000005</v>
+        <v>-0.1668000000000012</v>
       </c>
       <c r="F22" t="n">
-        <v>-13.2862</v>
+        <v>-11.9071</v>
       </c>
       <c r="G22" t="n">
         <v>1.101499999999999</v>
@@ -2170,13 +2170,13 @@
         <v>12.5502</v>
       </c>
       <c r="S22" t="n">
-        <v>-8.5503</v>
+        <v>-7.1713</v>
       </c>
       <c r="T22" t="n">
         <v>-3.8651</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.685</v>
+        <v>-3.3061</v>
       </c>
       <c r="V22" t="n">
         <v>-5.038600000000001</v>
